--- a/Financial Analysis/SRPT.xlsx
+++ b/Financial Analysis/SRPT.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E321596B-8946-463C-9CD4-51263E2AF500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE0567D-672E-4F16-B7B0-02A5E0C00B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{79CAE26F-8736-4C5E-9FC6-A2D7A01B0567}"/>
   </bookViews>
@@ -24,17 +24,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -938,7 +927,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -962,6 +951,13 @@
     <font>
       <b/>
       <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1112,7 +1108,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1158,6 +1154,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1870,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>13</v>
+        <v>19.04</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
@@ -1885,10 +1889,10 @@
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>97</v>
+        <v>100.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
@@ -1913,7 +1917,7 @@
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>1261</v>
+        <v>1907.808</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
@@ -1928,10 +1932,11 @@
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <v>786</v>
+        <f>613.1+237.9</f>
+        <v>851</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
@@ -1946,10 +1951,11 @@
         <v>4</v>
       </c>
       <c r="L6" s="2">
-        <v>1138</v>
+        <f>1035.1</f>
+        <v>1035.0999999999999</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
@@ -1968,7 +1974,7 @@
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>1613</v>
+        <v>2091.9079999999999</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
@@ -2471,13 +2477,13 @@
         <f t="shared" ref="X3:Z3" si="9">+X6/3.2</f>
         <v>88.078437499999993</v>
       </c>
-      <c r="Y3" s="5">
+      <c r="Y3" s="31">
         <f t="shared" si="9"/>
         <v>46.875</v>
       </c>
       <c r="Z3" s="5">
         <f t="shared" si="9"/>
-        <v>62.5</v>
+        <v>48.4375</v>
       </c>
       <c r="AP3" s="2">
         <f>+AP6/3.2</f>
@@ -2485,7 +2491,7 @@
       </c>
       <c r="AQ3" s="2">
         <f>+AQ6/3.2</f>
-        <v>314.64093750000001</v>
+        <v>300.57843750000001</v>
       </c>
       <c r="AR3">
         <v>800</v>
@@ -2537,60 +2543,60 @@
         <f t="shared" ref="X4:Z4" si="10">+W4+X3</f>
         <v>805.26593749999995</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="Y4" s="32">
         <f t="shared" si="10"/>
         <v>852.14093749999995</v>
       </c>
       <c r="Z4" s="2">
         <f t="shared" si="10"/>
-        <v>914.64093749999995</v>
+        <v>900.57843749999995</v>
       </c>
       <c r="AP4" s="2">
         <v>600</v>
       </c>
       <c r="AQ4" s="2">
         <f>+AP4+AQ3</f>
-        <v>914.64093750000006</v>
+        <v>900.57843750000006</v>
       </c>
       <c r="AR4" s="2">
         <f>+AQ4+AR3</f>
-        <v>1714.6409375000001</v>
+        <v>1700.5784375000001</v>
       </c>
       <c r="AS4" s="2">
         <f t="shared" ref="AS4:AX4" si="11">+AR4+AS3</f>
-        <v>2514.6409375000003</v>
+        <v>2500.5784375000003</v>
       </c>
       <c r="AT4" s="2">
         <f t="shared" si="11"/>
-        <v>3314.6409375000003</v>
+        <v>3300.5784375000003</v>
       </c>
       <c r="AU4" s="2">
         <f t="shared" si="11"/>
-        <v>4114.6409375000003</v>
+        <v>4100.5784375000003</v>
       </c>
       <c r="AV4" s="2">
         <f t="shared" si="11"/>
-        <v>4914.6409375000003</v>
+        <v>4900.5784375000003</v>
       </c>
       <c r="AW4" s="2">
         <f t="shared" si="11"/>
-        <v>5714.6409375000003</v>
+        <v>5700.5784375000003</v>
       </c>
       <c r="AX4" s="2">
         <f t="shared" si="11"/>
-        <v>6514.6409375000003</v>
+        <v>6500.5784375000003</v>
       </c>
       <c r="AY4" s="2">
         <f t="shared" ref="AY4" si="12">+AX4+AY3</f>
-        <v>7314.6409375000003</v>
+        <v>7300.5784375000003</v>
       </c>
       <c r="AZ4" s="2">
         <f t="shared" ref="AZ4" si="13">+AY4+AZ3</f>
-        <v>8114.6409375000003</v>
+        <v>8100.5784375000003</v>
       </c>
       <c r="BA4" s="2">
         <f t="shared" ref="BA4" si="14">+AZ4+BA3</f>
-        <v>8914.6409375000003</v>
+        <v>8900.5784375000003</v>
       </c>
     </row>
     <row r="5" spans="1:53" x14ac:dyDescent="0.25">
@@ -2601,7 +2607,7 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
+      <c r="Y5" s="33"/>
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2650,11 +2656,11 @@
       <c r="X6" s="2">
         <v>281.851</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y6" s="32">
         <v>150</v>
       </c>
       <c r="Z6" s="2">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="AO6" s="2">
         <f>SUM(O6:R6)</f>
@@ -2666,7 +2672,7 @@
       </c>
       <c r="AQ6" s="2">
         <f>SUM(W6:Z6)</f>
-        <v>1006.851</v>
+        <v>961.851</v>
       </c>
       <c r="AR6" s="2">
         <v>50</v>
@@ -2747,13 +2753,12 @@
       <c r="X7" s="2">
         <v>231.27199999999999</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y7" s="32">
         <f>+U7</f>
         <v>248.8</v>
       </c>
       <c r="Z7" s="2">
-        <f>+V7</f>
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="AH7" s="2">
         <f t="shared" ref="AH7:AN7" si="15">+AH13</f>
@@ -2793,47 +2798,47 @@
       </c>
       <c r="AQ7" s="2">
         <f t="shared" ref="AQ7" si="18">SUM(W7:Z7)</f>
-        <v>971.072</v>
+        <v>962.072</v>
       </c>
       <c r="AR7" s="2">
         <f>+AQ7*0.99</f>
-        <v>961.36127999999997</v>
+        <v>952.45128</v>
       </c>
       <c r="AS7" s="2">
         <f t="shared" ref="AS7:BA7" si="19">+AR7*0.99</f>
-        <v>951.74766719999991</v>
+        <v>942.92676719999997</v>
       </c>
       <c r="AT7" s="2">
         <f t="shared" si="19"/>
-        <v>942.23019052799987</v>
+        <v>933.49749952799993</v>
       </c>
       <c r="AU7" s="2">
         <f t="shared" si="19"/>
-        <v>932.80788862271982</v>
+        <v>924.16252453271989</v>
       </c>
       <c r="AV7" s="2">
         <f t="shared" si="19"/>
-        <v>923.4798097364926</v>
+        <v>914.92089928739267</v>
       </c>
       <c r="AW7" s="2">
         <f t="shared" si="19"/>
-        <v>914.24501163912771</v>
+        <v>905.77169029451875</v>
       </c>
       <c r="AX7" s="2">
         <f t="shared" si="19"/>
-        <v>905.10256152273644</v>
+        <v>896.71397339157352</v>
       </c>
       <c r="AY7" s="2">
         <f t="shared" si="19"/>
-        <v>896.05153590750911</v>
+        <v>887.74683365765782</v>
       </c>
       <c r="AZ7" s="2">
         <f t="shared" si="19"/>
-        <v>887.09102054843402</v>
+        <v>878.8693653210812</v>
       </c>
       <c r="BA7" s="2">
         <f t="shared" si="19"/>
-        <v>878.22011034294962</v>
+        <v>870.08067166787043</v>
       </c>
     </row>
     <row r="8" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2970,12 +2975,11 @@
         <v>513.12300000000005</v>
       </c>
       <c r="Y11" s="2">
-        <f>+Y7+Y6</f>
-        <v>398.8</v>
+        <v>370</v>
       </c>
       <c r="Z11" s="2">
         <f>+Z7+Z6</f>
-        <v>454</v>
+        <v>400</v>
       </c>
       <c r="AO11" s="2">
         <f t="shared" ref="AO11:AP11" si="20">+AO7+AO6</f>
@@ -2987,47 +2991,47 @@
       </c>
       <c r="AQ11" s="2">
         <f>+AQ7+AQ6</f>
-        <v>1977.923</v>
+        <v>1923.923</v>
       </c>
       <c r="AR11" s="2">
         <f t="shared" ref="AR11:BA11" si="21">+AR7+AR6</f>
-        <v>1011.36128</v>
+        <v>1002.45128</v>
       </c>
       <c r="AS11" s="2">
         <f t="shared" si="21"/>
-        <v>1051.7476671999998</v>
+        <v>1042.9267672000001</v>
       </c>
       <c r="AT11" s="2">
         <f t="shared" si="21"/>
-        <v>1092.2301905279999</v>
+        <v>1083.4974995279999</v>
       </c>
       <c r="AU11" s="2">
         <f t="shared" si="21"/>
-        <v>1132.8078886227199</v>
+        <v>1124.16252453272</v>
       </c>
       <c r="AV11" s="2">
         <f t="shared" si="21"/>
-        <v>1173.4798097364926</v>
+        <v>1164.9208992873928</v>
       </c>
       <c r="AW11" s="2">
         <f t="shared" si="21"/>
-        <v>1214.2450116391278</v>
+        <v>1205.7716902945187</v>
       </c>
       <c r="AX11" s="2">
         <f t="shared" si="21"/>
-        <v>1205.1025615227363</v>
+        <v>1196.7139733915735</v>
       </c>
       <c r="AY11" s="2">
         <f t="shared" si="21"/>
-        <v>1196.0515359075091</v>
+        <v>1187.7468336576578</v>
       </c>
       <c r="AZ11" s="2">
         <f t="shared" si="21"/>
-        <v>1187.091020548434</v>
+        <v>1178.8693653210812</v>
       </c>
       <c r="BA11" s="2">
         <f t="shared" si="21"/>
-        <v>1178.2201103429497</v>
+        <v>1170.0806716678703</v>
       </c>
     </row>
     <row r="12" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3083,12 +3087,10 @@
         <v>97.968000000000004</v>
       </c>
       <c r="Y12" s="2">
-        <f>AVERAGE(U12:X12)</f>
-        <v>72.239249999999998</v>
+        <v>29.3</v>
       </c>
       <c r="Z12" s="2">
-        <f>AVERAGE(V12:Y12)</f>
-        <v>80.948812500000003</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:53" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3158,11 +3160,11 @@
       </c>
       <c r="Y13" s="6">
         <f t="shared" si="22"/>
-        <v>471.03925000000004</v>
+        <v>399.3</v>
       </c>
       <c r="Z13" s="6">
         <f t="shared" si="22"/>
-        <v>534.94881250000003</v>
+        <v>425</v>
       </c>
       <c r="AH13" s="6">
         <v>5.4</v>
@@ -3195,47 +3197,47 @@
       </c>
       <c r="AQ13" s="6">
         <f t="shared" si="23"/>
-        <v>1977.923</v>
+        <v>1923.923</v>
       </c>
       <c r="AR13" s="6">
         <f t="shared" ref="AR13:BA13" si="24">+AR11+AR12</f>
-        <v>1011.36128</v>
+        <v>1002.45128</v>
       </c>
       <c r="AS13" s="6">
         <f t="shared" si="24"/>
-        <v>1051.7476671999998</v>
+        <v>1042.9267672000001</v>
       </c>
       <c r="AT13" s="6">
         <f t="shared" si="24"/>
-        <v>1092.2301905279999</v>
+        <v>1083.4974995279999</v>
       </c>
       <c r="AU13" s="6">
         <f t="shared" si="24"/>
-        <v>1132.8078886227199</v>
+        <v>1124.16252453272</v>
       </c>
       <c r="AV13" s="6">
         <f t="shared" si="24"/>
-        <v>1173.4798097364926</v>
+        <v>1164.9208992873928</v>
       </c>
       <c r="AW13" s="6">
         <f t="shared" si="24"/>
-        <v>1214.2450116391278</v>
+        <v>1205.7716902945187</v>
       </c>
       <c r="AX13" s="6">
         <f t="shared" si="24"/>
-        <v>1205.1025615227363</v>
+        <v>1196.7139733915735</v>
       </c>
       <c r="AY13" s="6">
         <f t="shared" si="24"/>
-        <v>1196.0515359075091</v>
+        <v>1187.7468336576578</v>
       </c>
       <c r="AZ13" s="6">
         <f t="shared" si="24"/>
-        <v>1187.091020548434</v>
+        <v>1178.8693653210812</v>
       </c>
       <c r="BA13" s="6">
         <f t="shared" si="24"/>
-        <v>1178.2201103429497</v>
+        <v>1170.0806716678703</v>
       </c>
     </row>
     <row r="14" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3291,12 +3293,11 @@
         <v>152.55799999999999</v>
       </c>
       <c r="Y14" s="2">
-        <f>+Y13*0.18</f>
-        <v>84.787064999999998</v>
+        <v>150.80000000000001</v>
       </c>
       <c r="Z14" s="2">
-        <f>+Z13*0.18</f>
-        <v>96.290786249999996</v>
+        <f>+Z13*0.3</f>
+        <v>127.5</v>
       </c>
       <c r="AO14" s="2">
         <f t="shared" ref="AO14:AO17" si="25">SUM(O14:R14)</f>
@@ -3308,47 +3309,47 @@
       </c>
       <c r="AQ14" s="2">
         <f t="shared" ref="AQ14" si="27">SUM(W14:Z14)</f>
-        <v>471.19985124999994</v>
+        <v>568.42200000000003</v>
       </c>
       <c r="AR14" s="2">
         <f>+AR13-AR15</f>
-        <v>151.70419200000003</v>
+        <v>150.36769200000003</v>
       </c>
       <c r="AS14" s="2">
         <f t="shared" ref="AS14:BA14" si="28">+AS13-AS15</f>
-        <v>157.76215007999997</v>
+        <v>156.43901507999999</v>
       </c>
       <c r="AT14" s="2">
         <f t="shared" si="28"/>
-        <v>163.83452857919997</v>
+        <v>162.52462492920006</v>
       </c>
       <c r="AU14" s="2">
         <f t="shared" si="28"/>
-        <v>169.92118329340803</v>
+        <v>168.62437867990798</v>
       </c>
       <c r="AV14" s="2">
         <f t="shared" si="28"/>
-        <v>176.02197146047388</v>
+        <v>174.73813489310896</v>
       </c>
       <c r="AW14" s="2">
         <f t="shared" si="28"/>
-        <v>182.13675174586911</v>
+        <v>180.86575354417778</v>
       </c>
       <c r="AX14" s="2">
         <f t="shared" si="28"/>
-        <v>180.76538422841054</v>
+        <v>179.50709600873608</v>
       </c>
       <c r="AY14" s="2">
         <f t="shared" si="28"/>
-        <v>179.40773038612645</v>
+        <v>178.16202504864873</v>
       </c>
       <c r="AZ14" s="2">
         <f t="shared" si="28"/>
-        <v>178.06365308226509</v>
+        <v>176.83040479816225</v>
       </c>
       <c r="BA14" s="2">
         <f t="shared" si="28"/>
-        <v>176.73301655144246</v>
+        <v>175.51210075018059</v>
       </c>
     </row>
     <row r="15" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3418,11 +3419,11 @@
       </c>
       <c r="Y15" s="2">
         <f t="shared" si="30"/>
-        <v>386.25218500000005</v>
+        <v>248.5</v>
       </c>
       <c r="Z15" s="2">
         <f t="shared" si="30"/>
-        <v>438.65802625000003</v>
+        <v>297.5</v>
       </c>
       <c r="AO15" s="2">
         <f>+AO13-AO14</f>
@@ -3434,47 +3435,47 @@
       </c>
       <c r="AQ15" s="2">
         <f>+AQ13-AQ14</f>
-        <v>1506.7231487500001</v>
+        <v>1355.501</v>
       </c>
       <c r="AR15" s="2">
         <f>+AR13*0.85</f>
-        <v>859.65708799999993</v>
+        <v>852.08358799999996</v>
       </c>
       <c r="AS15" s="2">
         <f t="shared" ref="AS15:BA15" si="31">+AS13*0.85</f>
-        <v>893.98551711999983</v>
+        <v>886.4877521200001</v>
       </c>
       <c r="AT15" s="2">
         <f t="shared" si="31"/>
-        <v>928.3956619487999</v>
+        <v>920.97287459879988</v>
       </c>
       <c r="AU15" s="2">
         <f t="shared" si="31"/>
-        <v>962.88670532931189</v>
+        <v>955.53814585281202</v>
       </c>
       <c r="AV15" s="2">
         <f t="shared" si="31"/>
-        <v>997.45783827601872</v>
+        <v>990.18276439428382</v>
       </c>
       <c r="AW15" s="2">
         <f t="shared" si="31"/>
-        <v>1032.1082598932587</v>
+        <v>1024.905936750341</v>
       </c>
       <c r="AX15" s="2">
         <f t="shared" si="31"/>
-        <v>1024.3371772943258</v>
+        <v>1017.2068773828374</v>
       </c>
       <c r="AY15" s="2">
         <f t="shared" si="31"/>
-        <v>1016.6438055213827</v>
+        <v>1009.5848086090091</v>
       </c>
       <c r="AZ15" s="2">
         <f t="shared" si="31"/>
-        <v>1009.0273674661689</v>
+        <v>1002.038960522919</v>
       </c>
       <c r="BA15" s="2">
         <f t="shared" si="31"/>
-        <v>1001.4870937915073</v>
+        <v>994.56857091768973</v>
       </c>
     </row>
     <row r="16" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3530,6 +3531,9 @@
       <c r="X16" s="2">
         <v>204.392</v>
       </c>
+      <c r="Y16" s="2">
+        <v>218.9</v>
+      </c>
       <c r="AO16" s="2">
         <f t="shared" si="25"/>
         <v>877.38699999999994</v>
@@ -3590,6 +3594,9 @@
       </c>
       <c r="X17" s="2">
         <v>137.89699999999999</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>91.9</v>
       </c>
       <c r="AO17" s="2">
         <f t="shared" si="25"/>
@@ -3711,7 +3718,7 @@
       </c>
       <c r="Y18" s="2">
         <f>+Y17+Y16</f>
-        <v>0</v>
+        <v>310.8</v>
       </c>
       <c r="Z18" s="2">
         <f>+Z17+Z16</f>
@@ -3837,11 +3844,11 @@
       </c>
       <c r="Y19" s="2">
         <f>+Y15-Y18</f>
-        <v>386.25218500000005</v>
+        <v>-62.300000000000011</v>
       </c>
       <c r="Z19" s="2">
         <f>+Z15-Z18</f>
-        <v>438.65802625000003</v>
+        <v>297.5</v>
       </c>
       <c r="AO19" s="2">
         <f>+AO15-AO18</f>
@@ -3853,47 +3860,47 @@
       </c>
       <c r="AQ19" s="2">
         <f>+AQ15-AQ18</f>
-        <v>948.25114875000008</v>
+        <v>797.029</v>
       </c>
       <c r="AR19" s="2">
         <f t="shared" ref="AR19" si="47">+AR15-AR18</f>
-        <v>357.03228799999994</v>
+        <v>349.45878799999997</v>
       </c>
       <c r="AS19" s="2">
         <f t="shared" ref="AS19" si="48">+AS15-AS18</f>
-        <v>441.62319711999982</v>
+        <v>434.12543212000008</v>
       </c>
       <c r="AT19" s="2">
         <f t="shared" ref="AT19" si="49">+AT15-AT18</f>
-        <v>521.26957394879992</v>
+        <v>513.84678659879978</v>
       </c>
       <c r="AU19" s="2">
         <f t="shared" ref="AU19" si="50">+AU15-AU18</f>
-        <v>596.4732261293118</v>
+        <v>589.12466665281204</v>
       </c>
       <c r="AV19" s="2">
         <f t="shared" ref="AV19" si="51">+AV15-AV18</f>
-        <v>667.68570699601867</v>
+        <v>660.41063311428377</v>
       </c>
       <c r="AW19" s="2">
         <f t="shared" ref="AW19" si="52">+AW15-AW18</f>
-        <v>735.31334174125868</v>
+        <v>728.11101859834093</v>
       </c>
       <c r="AX19" s="2">
         <f t="shared" ref="AX19" si="53">+AX15-AX18</f>
-        <v>757.22175095752573</v>
+        <v>750.09145104603738</v>
       </c>
       <c r="AY19" s="2">
         <f t="shared" ref="AY19" si="54">+AY15-AY18</f>
-        <v>776.23992181826259</v>
+        <v>769.18092490588901</v>
       </c>
       <c r="AZ19" s="2">
         <f t="shared" ref="AZ19" si="55">+AZ15-AZ18</f>
-        <v>792.66387213336088</v>
+        <v>785.67546519011091</v>
       </c>
       <c r="BA19" s="2">
         <f t="shared" ref="BA19" si="56">+BA15-BA18</f>
-        <v>806.75994799197997</v>
+        <v>799.84142511816253</v>
       </c>
     </row>
     <row r="20" spans="2:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3947,6 +3954,9 @@
       </c>
       <c r="X20" s="2">
         <v>38.061</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>-90.7</v>
       </c>
       <c r="AO20" s="2">
         <f t="shared" ref="AO20" si="57">SUM(O20:R20)</f>
@@ -4024,11 +4034,11 @@
       </c>
       <c r="Y21" s="2">
         <f>+Y19+Y20</f>
-        <v>386.25218500000005</v>
+        <v>-153</v>
       </c>
       <c r="Z21" s="2">
         <f>+Z19+Z20</f>
-        <v>438.65802625000003</v>
+        <v>297.5</v>
       </c>
       <c r="AO21" s="2">
         <f>+AO19+AO20</f>
@@ -4040,47 +4050,47 @@
       </c>
       <c r="AQ21" s="2">
         <f>+AQ19+AQ20</f>
-        <v>948.25114875000008</v>
+        <v>797.029</v>
       </c>
       <c r="AR21" s="2">
         <f t="shared" ref="AR21:BA21" si="60">+AR19+AR20</f>
-        <v>357.03228799999994</v>
+        <v>349.45878799999997</v>
       </c>
       <c r="AS21" s="2">
         <f t="shared" si="60"/>
-        <v>441.62319711999982</v>
+        <v>434.12543212000008</v>
       </c>
       <c r="AT21" s="2">
         <f t="shared" si="60"/>
-        <v>521.26957394879992</v>
+        <v>513.84678659879978</v>
       </c>
       <c r="AU21" s="2">
         <f t="shared" si="60"/>
-        <v>596.4732261293118</v>
+        <v>589.12466665281204</v>
       </c>
       <c r="AV21" s="2">
         <f t="shared" si="60"/>
-        <v>667.68570699601867</v>
+        <v>660.41063311428377</v>
       </c>
       <c r="AW21" s="2">
         <f t="shared" si="60"/>
-        <v>735.31334174125868</v>
+        <v>728.11101859834093</v>
       </c>
       <c r="AX21" s="2">
         <f t="shared" si="60"/>
-        <v>757.22175095752573</v>
+        <v>750.09145104603738</v>
       </c>
       <c r="AY21" s="2">
         <f t="shared" si="60"/>
-        <v>776.23992181826259</v>
+        <v>769.18092490588901</v>
       </c>
       <c r="AZ21" s="2">
         <f t="shared" si="60"/>
-        <v>792.66387213336088</v>
+        <v>785.67546519011091</v>
       </c>
       <c r="BA21" s="2">
         <f t="shared" si="60"/>
-        <v>806.75994799197997</v>
+        <v>799.84142511816253</v>
       </c>
     </row>
     <row r="22" spans="2:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4136,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="Y22" s="2">
-        <v>0</v>
+        <v>-14.1</v>
       </c>
       <c r="Z22" s="2">
         <v>0</v>
@@ -4151,47 +4161,47 @@
       </c>
       <c r="AQ22" s="2">
         <f>+AQ21*0.2</f>
-        <v>189.65022975000002</v>
+        <v>159.4058</v>
       </c>
       <c r="AR22" s="2">
         <f t="shared" ref="AR22:BA22" si="63">+AR21*0.2</f>
-        <v>71.406457599999996</v>
+        <v>69.891757599999991</v>
       </c>
       <c r="AS22" s="2">
         <f t="shared" si="63"/>
-        <v>88.324639423999969</v>
+        <v>86.82508642400002</v>
       </c>
       <c r="AT22" s="2">
         <f t="shared" si="63"/>
-        <v>104.25391478975999</v>
+        <v>102.76935731975996</v>
       </c>
       <c r="AU22" s="2">
         <f t="shared" si="63"/>
-        <v>119.29464522586237</v>
+        <v>117.82493333056242</v>
       </c>
       <c r="AV22" s="2">
         <f t="shared" si="63"/>
-        <v>133.53714139920373</v>
+        <v>132.08212662285675</v>
       </c>
       <c r="AW22" s="2">
         <f t="shared" si="63"/>
-        <v>147.06266834825175</v>
+        <v>145.62220371966819</v>
       </c>
       <c r="AX22" s="2">
         <f t="shared" si="63"/>
-        <v>151.44435019150515</v>
+        <v>150.01829020920749</v>
       </c>
       <c r="AY22" s="2">
         <f t="shared" si="63"/>
-        <v>155.24798436365253</v>
+        <v>153.83618498117781</v>
       </c>
       <c r="AZ22" s="2">
         <f t="shared" si="63"/>
-        <v>158.53277442667218</v>
+        <v>157.13509303802221</v>
       </c>
       <c r="BA22" s="2">
         <f t="shared" si="63"/>
-        <v>161.35198959839602</v>
+        <v>159.96828502363252</v>
       </c>
     </row>
     <row r="23" spans="2:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4261,11 +4271,11 @@
       </c>
       <c r="Y23" s="2">
         <f>+Y21-Y22</f>
-        <v>386.25218500000005</v>
+        <v>-138.9</v>
       </c>
       <c r="Z23" s="2">
         <f>+Z21-Z22</f>
-        <v>438.65802625000003</v>
+        <v>297.5</v>
       </c>
       <c r="AO23" s="2">
         <f>+AO21-AO22</f>
@@ -4277,47 +4287,47 @@
       </c>
       <c r="AQ23" s="2">
         <f>+AQ21-AQ22</f>
-        <v>758.60091900000009</v>
+        <v>637.6232</v>
       </c>
       <c r="AR23" s="2">
         <f t="shared" ref="AR23:BA23" si="65">+AR21-AR22</f>
-        <v>285.62583039999993</v>
+        <v>279.56703039999996</v>
       </c>
       <c r="AS23" s="2">
         <f t="shared" si="65"/>
-        <v>353.29855769599988</v>
+        <v>347.30034569600008</v>
       </c>
       <c r="AT23" s="2">
         <f t="shared" si="65"/>
-        <v>417.01565915903996</v>
+        <v>411.07742927903985</v>
       </c>
       <c r="AU23" s="2">
         <f t="shared" si="65"/>
-        <v>477.17858090344942</v>
+        <v>471.29973332224961</v>
       </c>
       <c r="AV23" s="2">
         <f t="shared" si="65"/>
-        <v>534.14856559681493</v>
+        <v>528.32850649142699</v>
       </c>
       <c r="AW23" s="2">
         <f t="shared" si="65"/>
-        <v>588.25067339300699</v>
+        <v>582.48881487867277</v>
       </c>
       <c r="AX23" s="2">
         <f t="shared" si="65"/>
-        <v>605.77740076602061</v>
+        <v>600.07316083682986</v>
       </c>
       <c r="AY23" s="2">
         <f t="shared" si="65"/>
-        <v>620.99193745461002</v>
+        <v>615.34473992471123</v>
       </c>
       <c r="AZ23" s="2">
         <f t="shared" si="65"/>
-        <v>634.13109770668871</v>
+        <v>628.54037215208871</v>
       </c>
       <c r="BA23" s="2">
         <f t="shared" si="65"/>
-        <v>645.40795839358395</v>
+        <v>639.87314009453007</v>
       </c>
     </row>
     <row r="24" spans="2:56" x14ac:dyDescent="0.25">
@@ -4378,55 +4388,55 @@
       </c>
       <c r="Y24" s="1">
         <f t="shared" si="66"/>
-        <v>3.622597235118127</v>
+        <v>-1.3862275449101797</v>
       </c>
       <c r="Z24" s="1">
         <f t="shared" si="66"/>
-        <v>4.1141032070941543</v>
+        <v>2.9690618762475047</v>
       </c>
       <c r="AQ24" s="1">
         <f>+AQ23/AQ25</f>
-        <v>6.9933893744123026</v>
+        <v>5.8781201025130443</v>
       </c>
       <c r="AR24" s="1">
         <f t="shared" ref="AR24:BA24" si="67">+AR23/AR25</f>
-        <v>2.6331271124877844</v>
+        <v>2.5772722532588452</v>
       </c>
       <c r="AS24" s="1">
         <f t="shared" si="67"/>
-        <v>3.2569883815107756</v>
+        <v>3.201692070874127</v>
       </c>
       <c r="AT24" s="1">
         <f t="shared" si="67"/>
-        <v>3.8443835311599086</v>
+        <v>3.7896401836296238</v>
       </c>
       <c r="AU24" s="1">
         <f t="shared" si="67"/>
-        <v>4.3990134124624278</v>
+        <v>4.3448174984074486</v>
       </c>
       <c r="AV24" s="1">
         <f t="shared" si="67"/>
-        <v>4.9242082489519596</v>
+        <v>4.8705542940375297</v>
       </c>
       <c r="AW24" s="1">
         <f t="shared" si="67"/>
-        <v>5.4229647048417773</v>
+        <v>5.3698472894764899</v>
       </c>
       <c r="AX24" s="1">
         <f t="shared" si="67"/>
-        <v>5.5845400811809336</v>
+        <v>5.5319538399693</v>
       </c>
       <c r="AY24" s="1">
         <f t="shared" si="67"/>
-        <v>5.7247998364088168</v>
+        <v>5.6727394576092998</v>
       </c>
       <c r="AZ24" s="1">
         <f t="shared" si="67"/>
-        <v>5.8459271134713262</v>
+        <v>5.7943873384598028</v>
       </c>
       <c r="BA24" s="1">
         <f t="shared" si="67"/>
-        <v>5.9498862252114231</v>
+        <v>5.8988618479500161</v>
       </c>
     </row>
     <row r="25" spans="2:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4482,12 +4492,11 @@
         <v>106.623</v>
       </c>
       <c r="Y25" s="2">
-        <f>+X25</f>
-        <v>106.623</v>
+        <v>100.2</v>
       </c>
       <c r="Z25" s="2">
         <f>+Y25</f>
-        <v>106.623</v>
+        <v>100.2</v>
       </c>
       <c r="AO25" s="2">
         <f>R25</f>
@@ -4568,11 +4577,11 @@
       </c>
       <c r="Y27" s="22">
         <f>+Y13/U13-1</f>
-        <v>8.2154147786499543E-3</v>
+        <v>-0.1453357334423514</v>
       </c>
       <c r="Z27" s="22">
         <f>+Z13/V13-1</f>
-        <v>-0.18756967066845875</v>
+        <v>-0.35454966550485612</v>
       </c>
       <c r="BD27" s="22"/>
     </row>
@@ -4610,11 +4619,11 @@
       </c>
       <c r="Y28" s="22">
         <f>+Y15/Y13</f>
-        <v>0.82000000000000006</v>
+        <v>0.6223390934134736</v>
       </c>
       <c r="Z28" s="22">
         <f>+Z15/Z13</f>
-        <v>0.82000000000000006</v>
+        <v>0.7</v>
       </c>
       <c r="AO28" s="22">
         <f t="shared" ref="AO28" si="71">+AO15/AO13</f>
@@ -4629,7 +4638,7 @@
       </c>
       <c r="BD28" s="2">
         <f>NPV(BD26,AR23:BA23)+Main!L5-Main!L6</f>
-        <v>2773.013654059022</v>
+        <v>2903.4715279898942</v>
       </c>
     </row>
     <row r="29" spans="2:56" x14ac:dyDescent="0.25">
@@ -4639,11 +4648,17 @@
       </c>
       <c r="AQ29" s="22">
         <f>+AQ13/AP13-1</f>
-        <v>0.10620111944305255</v>
+        <v>7.6000317667692885E-2</v>
       </c>
       <c r="BD29" s="1">
         <f>+BD28/Main!L3</f>
-        <v>28.587769629474455</v>
+        <v>28.976761756386168</v>
+      </c>
+    </row>
+    <row r="30" spans="2:56" x14ac:dyDescent="0.25">
+      <c r="BD30" s="30">
+        <f>BD29/Main!L2-1</f>
+        <v>0.52188874770935767</v>
       </c>
     </row>
     <row r="31" spans="2:56" x14ac:dyDescent="0.25">
